--- a/2.RD_CGE/Input_CGE/Projection.xlsx
+++ b/2.RD_CGE/Input_CGE/Projection.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_w-t\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimc0\GUIDE_GLOBAL_CGE\2.RD_CGE\Input_CGE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5158032-1B8D-4FF1-93FF-8CE6F616FC37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD974B4A-D5FD-4DDF-912C-A9E082D60467}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="907" activeTab="12" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9684" tabRatio="907" activeTab="9" xr2:uid="{F15F39B2-9333-4C81-A44C-4FDD4B656403}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseyear" sheetId="12" r:id="rId1"/>
@@ -537,6 +537,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>NDC</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5206,6 +5231,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>NZ</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -23057,8 +23107,8 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>568036</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>526472</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>6927</xdr:rowOff>
     </xdr:from>
@@ -23136,16 +23186,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>242454</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>166254</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>547254</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>117764</xdr:rowOff>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>471054</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>79664</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25051,128 +25101,128 @@
         <v>1</v>
       </c>
       <c r="C2" s="11">
-        <f>B2-B2*0.02</f>
-        <v>0.98</v>
+        <f>B2-B2*0.015</f>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D2" s="11">
-        <f t="shared" ref="D2:AG10" si="0">C2-C2*0.02</f>
-        <v>0.96040000000000003</v>
+        <f t="shared" ref="D2:AG10" si="0">C2-C2*0.015</f>
+        <v>0.970225</v>
       </c>
       <c r="E2" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F2" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G2" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H2" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I2" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J2" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K2" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L2" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M2" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N2" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O2" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P2" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q2" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R2" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S2" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T2" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U2" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V2" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W2" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X2" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y2" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z2" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA2" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB2" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC2" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD2" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE2" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF2" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG2" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
@@ -25183,128 +25233,128 @@
         <v>1</v>
       </c>
       <c r="C3" s="11">
-        <f t="shared" ref="C3:R18" si="1">B3-B3*0.02</f>
-        <v>0.98</v>
+        <f t="shared" ref="C3:R18" si="1">B3-B3*0.015</f>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="1"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E3" s="11">
         <f t="shared" si="1"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" si="1"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G3" s="11">
         <f t="shared" si="1"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H3" s="11">
         <f t="shared" si="1"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I3" s="11">
         <f t="shared" si="1"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" si="1"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K3" s="11">
         <f t="shared" si="1"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L3" s="11">
         <f t="shared" si="1"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M3" s="11">
         <f t="shared" si="1"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N3" s="11">
         <f t="shared" si="1"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O3" s="11">
         <f t="shared" si="1"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P3" s="11">
         <f t="shared" si="1"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="1"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R3" s="11">
         <f t="shared" si="1"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S3" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T3" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U3" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V3" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W3" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X3" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y3" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z3" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA3" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB3" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC3" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD3" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE3" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF3" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG3" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -25316,127 +25366,127 @@
       </c>
       <c r="C4" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E4" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F4" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G4" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H4" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I4" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J4" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K4" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M4" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N4" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O4" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P4" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q4" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R4" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T4" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U4" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V4" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W4" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X4" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y4" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z4" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA4" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB4" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC4" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD4" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE4" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF4" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG4" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -25448,127 +25498,127 @@
       </c>
       <c r="C5" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E5" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F5" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G5" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I5" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J5" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K5" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N5" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O5" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P5" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q5" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R5" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S5" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T5" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V5" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W5" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X5" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y5" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z5" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA5" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB5" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC5" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD5" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE5" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF5" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG5" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -25580,127 +25630,127 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D6" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E6" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G6" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J6" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N6" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O6" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P6" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q6" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R6" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S6" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T6" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V6" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W6" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X6" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y6" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z6" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA6" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB6" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC6" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD6" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE6" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF6" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG6" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -25712,127 +25762,127 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E7" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G7" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I7" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J7" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N7" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O7" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P7" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q7" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R7" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S7" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T7" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V7" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W7" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X7" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y7" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z7" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA7" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB7" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC7" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD7" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE7" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF7" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG7" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -25844,127 +25894,127 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E8" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G8" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I8" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J8" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N8" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O8" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P8" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q8" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R8" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S8" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T8" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V8" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W8" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X8" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y8" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z8" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA8" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB8" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC8" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD8" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE8" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF8" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG8" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -25976,127 +26026,127 @@
       </c>
       <c r="C9" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E9" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G9" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I9" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J9" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L9" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M9" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N9" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O9" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P9" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q9" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R9" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S9" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T9" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U9" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V9" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W9" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X9" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y9" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z9" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA9" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB9" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC9" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD9" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE9" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF9" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG9" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -26108,127 +26158,127 @@
       </c>
       <c r="C10" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D10" s="11">
         <f t="shared" si="0"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E10" s="11">
         <f t="shared" si="0"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G10" s="11">
         <f t="shared" si="0"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H10" s="11">
         <f t="shared" si="0"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="0"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J10" s="11">
         <f t="shared" si="0"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K10" s="11">
         <f t="shared" si="0"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L10" s="11">
         <f t="shared" si="0"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M10" s="11">
         <f t="shared" si="0"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N10" s="11">
         <f t="shared" si="0"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O10" s="11">
         <f t="shared" si="0"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P10" s="11">
         <f t="shared" si="0"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q10" s="11">
         <f t="shared" si="0"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R10" s="11">
         <f t="shared" si="0"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S10" s="11">
         <f t="shared" si="0"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T10" s="11">
         <f t="shared" si="0"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="0"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V10" s="11">
         <f t="shared" si="0"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W10" s="11">
         <f t="shared" si="0"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X10" s="11">
         <f t="shared" si="0"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y10" s="11">
         <f t="shared" si="0"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z10" s="11">
         <f t="shared" si="0"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA10" s="11">
         <f t="shared" si="0"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB10" s="11">
         <f t="shared" si="0"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC10" s="11">
         <f t="shared" si="0"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD10" s="11">
         <f t="shared" si="0"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE10" s="11">
         <f t="shared" si="0"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF10" s="11">
         <f t="shared" si="0"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG10" s="11">
         <f t="shared" si="0"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -26240,127 +26290,127 @@
       </c>
       <c r="C11" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D11" s="11">
-        <f t="shared" ref="D11:AG18" si="2">C11-C11*0.02</f>
-        <v>0.96040000000000003</v>
+        <f t="shared" ref="D11:AG18" si="2">C11-C11*0.015</f>
+        <v>0.970225</v>
       </c>
       <c r="E11" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G11" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J11" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L11" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M11" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N11" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O11" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P11" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q11" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R11" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S11" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T11" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U11" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V11" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W11" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X11" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y11" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z11" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA11" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB11" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC11" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD11" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE11" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF11" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG11" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -26372,127 +26422,127 @@
       </c>
       <c r="C12" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D12" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E12" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G12" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H12" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I12" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J12" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L12" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M12" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N12" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O12" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P12" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q12" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R12" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S12" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T12" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U12" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V12" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W12" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X12" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y12" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z12" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA12" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB12" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC12" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD12" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE12" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF12" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG12" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -26504,127 +26554,127 @@
       </c>
       <c r="C13" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D13" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E13" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G13" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J13" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L13" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M13" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N13" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O13" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P13" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q13" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R13" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S13" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T13" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U13" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V13" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W13" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X13" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y13" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z13" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA13" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB13" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC13" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD13" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE13" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF13" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG13" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -26636,127 +26686,127 @@
       </c>
       <c r="C14" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D14" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E14" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G14" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H14" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I14" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J14" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K14" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L14" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M14" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N14" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O14" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P14" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q14" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R14" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S14" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T14" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U14" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V14" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W14" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X14" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y14" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z14" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA14" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB14" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC14" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD14" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE14" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF14" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG14" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -26768,127 +26818,127 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G15" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I15" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J15" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N15" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S15" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T15" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U15" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V15" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W15" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X15" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y15" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z15" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA15" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB15" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC15" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD15" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE15" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF15" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG15" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -26900,127 +26950,127 @@
       </c>
       <c r="C16" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D16" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E16" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G16" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I16" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J16" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K16" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L16" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M16" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N16" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O16" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P16" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q16" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S16" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T16" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U16" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V16" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W16" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X16" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y16" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z16" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA16" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB16" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC16" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD16" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE16" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF16" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG16" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
@@ -27032,127 +27082,127 @@
       </c>
       <c r="C17" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D17" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K17" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L17" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M17" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N17" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O17" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P17" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q17" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R17" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S17" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T17" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U17" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V17" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W17" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X17" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y17" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z17" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA17" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB17" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC17" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE17" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF17" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG17" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
@@ -27164,127 +27214,127 @@
       </c>
       <c r="C18" s="11">
         <f t="shared" si="1"/>
-        <v>0.98</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="D18" s="11">
         <f t="shared" si="2"/>
-        <v>0.96040000000000003</v>
+        <v>0.970225</v>
       </c>
       <c r="E18" s="11">
         <f t="shared" si="2"/>
-        <v>0.94119200000000003</v>
+        <v>0.95567162500000002</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="2"/>
-        <v>0.92236815999999999</v>
+        <v>0.94133655062499999</v>
       </c>
       <c r="G18" s="11">
         <f t="shared" si="2"/>
-        <v>0.90392079680000004</v>
+        <v>0.92721650236562503</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="2"/>
-        <v>0.88584238086400002</v>
+        <v>0.91330825483014066</v>
       </c>
       <c r="I18" s="11">
         <f t="shared" si="2"/>
-        <v>0.86812553324672004</v>
+        <v>0.89960863100768851</v>
       </c>
       <c r="J18" s="11">
         <f t="shared" si="2"/>
-        <v>0.8507630225817856</v>
+        <v>0.88611450154257321</v>
       </c>
       <c r="K18" s="11">
         <f t="shared" si="2"/>
-        <v>0.83374776213014989</v>
+        <v>0.87282278401943458</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="2"/>
-        <v>0.81707280688754691</v>
+        <v>0.85973044225914308</v>
       </c>
       <c r="M18" s="11">
         <f t="shared" si="2"/>
-        <v>0.80073135074979596</v>
+        <v>0.84683448562525598</v>
       </c>
       <c r="N18" s="11">
         <f t="shared" si="2"/>
-        <v>0.78471672373480006</v>
+        <v>0.83413196834087711</v>
       </c>
       <c r="O18" s="11">
         <f t="shared" si="2"/>
-        <v>0.76902238926010402</v>
+        <v>0.82161998881576392</v>
       </c>
       <c r="P18" s="11">
         <f t="shared" si="2"/>
-        <v>0.75364194147490193</v>
+        <v>0.80929568898352744</v>
       </c>
       <c r="Q18" s="11">
         <f t="shared" si="2"/>
-        <v>0.73856910264540387</v>
+        <v>0.79715625364877452</v>
       </c>
       <c r="R18" s="11">
         <f t="shared" si="2"/>
-        <v>0.72379772059249581</v>
+        <v>0.78519890984404295</v>
       </c>
       <c r="S18" s="11">
         <f t="shared" si="2"/>
-        <v>0.70932176618064591</v>
+        <v>0.77342092619638225</v>
       </c>
       <c r="T18" s="11">
         <f t="shared" si="2"/>
-        <v>0.69513533085703294</v>
+        <v>0.76181961230343653</v>
       </c>
       <c r="U18" s="11">
         <f t="shared" si="2"/>
-        <v>0.68123262423989228</v>
+        <v>0.75039231811888496</v>
       </c>
       <c r="V18" s="11">
         <f t="shared" si="2"/>
-        <v>0.66760797175509445</v>
+        <v>0.73913643334710166</v>
       </c>
       <c r="W18" s="11">
         <f t="shared" si="2"/>
-        <v>0.65425581231999252</v>
+        <v>0.72804938684689513</v>
       </c>
       <c r="X18" s="11">
         <f t="shared" si="2"/>
-        <v>0.64117069607359267</v>
+        <v>0.71712864604419169</v>
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="2"/>
-        <v>0.62834728215212077</v>
+        <v>0.7063717163535288</v>
       </c>
       <c r="Z18" s="11">
         <f t="shared" si="2"/>
-        <v>0.61578033650907837</v>
+        <v>0.6957761406082259</v>
       </c>
       <c r="AA18" s="11">
         <f t="shared" si="2"/>
-        <v>0.60346472977889676</v>
+        <v>0.68533949849910247</v>
       </c>
       <c r="AB18" s="11">
         <f t="shared" si="2"/>
-        <v>0.59139543518331883</v>
+        <v>0.67505940602161596</v>
       </c>
       <c r="AC18" s="11">
         <f t="shared" si="2"/>
-        <v>0.57956752647965248</v>
+        <v>0.66493351493129171</v>
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="2"/>
-        <v>0.56797617595005945</v>
+        <v>0.65495951220732229</v>
       </c>
       <c r="AE18" s="11">
         <f t="shared" si="2"/>
-        <v>0.55661665243105829</v>
+        <v>0.64513511952421243</v>
       </c>
       <c r="AF18" s="11">
         <f t="shared" si="2"/>
-        <v>0.54548431938243713</v>
+        <v>0.63545809273134923</v>
       </c>
       <c r="AG18" s="11">
         <f t="shared" si="2"/>
-        <v>0.53457463299478836</v>
+        <v>0.62592622134037901</v>
       </c>
     </row>
   </sheetData>
